--- a/src/technology/template/template.xlsx
+++ b/src/technology/template/template.xlsx
@@ -1,30 +1,31 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rhanes\GitHub\tyche\src\technology\template\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20F57150-3A38-4E84-A463-467CAF88866C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCF2C777-086D-4380-BB78-7CD97F28FE2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="810" yWindow="-120" windowWidth="28110" windowHeight="16440" activeTab="5" xr2:uid="{277ED3FD-2B20-4A36-BB03-16AF83BDC75C}"/>
+    <workbookView xWindow="14760" yWindow="90" windowWidth="21570" windowHeight="20805" activeTab="1" xr2:uid="{277ED3FD-2B20-4A36-BB03-16AF83BDC75C}"/>
   </bookViews>
   <sheets>
     <sheet name="indices" sheetId="1" r:id="rId1"/>
-    <sheet name="functions" sheetId="2" r:id="rId2"/>
-    <sheet name="designs" sheetId="3" r:id="rId3"/>
-    <sheet name="parameters" sheetId="4" r:id="rId4"/>
-    <sheet name="results" sheetId="5" r:id="rId5"/>
-    <sheet name="tranches" sheetId="6" r:id="rId6"/>
-    <sheet name="investments" sheetId="7" r:id="rId7"/>
+    <sheet name="metadata" sheetId="8" r:id="rId2"/>
+    <sheet name="functions" sheetId="2" r:id="rId3"/>
+    <sheet name="designs" sheetId="3" r:id="rId4"/>
+    <sheet name="parameters" sheetId="4" r:id="rId5"/>
+    <sheet name="results" sheetId="5" r:id="rId6"/>
+    <sheet name="tranches" sheetId="6" r:id="rId7"/>
+    <sheet name="investments" sheetId="7" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">designs!$A$1:$G$925</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">designs!$A$1:$G$925</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">indices!$A$1:$F$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">parameters!$A$1:$G$837</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">parameters!$A$1:$G$837</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -47,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8455" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8528" uniqueCount="258">
   <si>
     <t>Category</t>
   </si>
@@ -816,6 +817,12 @@
   <si>
     <t>Component B2 No Funding</t>
   </si>
+  <si>
+    <t>Kind</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
 </sst>
 </file>
 
@@ -870,9 +877,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -910,7 +917,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -1016,7 +1023,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1158,7 +1165,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1664,6 +1671,313 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2B840AB5-9F0E-41EA-9F17-3461080DE366}">
+  <dimension ref="A1:C36"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="33" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>256</v>
+      </c>
+      <c r="B1" t="s">
+        <v>257</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>1</v>
+      </c>
+      <c r="B14" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>1</v>
+      </c>
+      <c r="B19" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>1</v>
+      </c>
+      <c r="B21" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>1</v>
+      </c>
+      <c r="B22" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>1</v>
+      </c>
+      <c r="B23" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B25" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>0</v>
+      </c>
+      <c r="B26" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>0</v>
+      </c>
+      <c r="B27" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>0</v>
+      </c>
+      <c r="B28" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>0</v>
+      </c>
+      <c r="B29" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>0</v>
+      </c>
+      <c r="B30" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>0</v>
+      </c>
+      <c r="B31" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>0</v>
+      </c>
+      <c r="B32" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>12</v>
+      </c>
+      <c r="B33" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>12</v>
+      </c>
+      <c r="B34" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>12</v>
+      </c>
+      <c r="B35" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>12</v>
+      </c>
+      <c r="B36" t="s">
+        <v>254</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A97C873A-D063-4744-8651-CEF648C63973}">
   <dimension ref="A1:H3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -1761,7 +2075,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7FB20890-62B7-47AF-BA68-650F053D99C5}">
   <dimension ref="A1:G925"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -20199,7 +20513,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9375A35C-8A58-4D70-9436-2E641DE51D25}">
   <dimension ref="A1:G837"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -37053,7 +37367,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08421A62-7A7F-4754-940E-DE21752714F2}">
   <dimension ref="A1:E17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -37324,7 +37638,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D89E1871-0EA4-4433-AFC4-28BCC91530B9}">
   <dimension ref="A1:D29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -37686,7 +38000,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD318B56-38BD-4E5D-86D7-782D60429334}">
   <dimension ref="A1:D50"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -38259,4 +38573,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{95965d95-ecc0-4720-b759-1f33c42ed7da}" enabled="1" method="Standard" siteId="{a0f29d7e-28cd-4f54-8442-7885aee7c080}" contentBits="0" removed="0"/>
+</clbl:labelList>
 </file>